--- a/data/definitions/TheoryCharacteristics.xlsx
+++ b/data/definitions/TheoryCharacteristics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzh-my.sharepoint.com/personal/maya_braun_uzh_ch/Documents/git/theory-database/definitions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ugentbe-my.sharepoint.com/personal/maya_braun_ugent_be/Documents/Documenten/GitHub/theory-database/data/definitions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{8FB7BD99-C685-44E8-85FC-99310A2CF596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E5E17AE-475A-4C70-893F-310ED229D6C8}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="8_{8FB7BD99-C685-44E8-85FC-99310A2CF596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AF9B53A-1FCD-4DCF-AEE7-A8CE9F427096}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{D4533F75-BB90-4810-8126-A526439C84A6}"/>
+    <workbookView xWindow="-28920" yWindow="3645" windowWidth="29040" windowHeight="15720" xr2:uid="{D4533F75-BB90-4810-8126-A526439C84A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="161">
   <si>
     <t>Theory</t>
   </si>
@@ -540,6 +540,9 @@
   </si>
   <si>
     <t>Stern, P.C., Dietz, T. Abel, T., Guagnano, G.A. &amp; Kalof, L. (1999). A Value-Belief-Norm Theory of Support for Social Movements: The Case of Environmentalism. Research in Human Ecology, 6(2), 81-97.</t>
+  </si>
+  <si>
+    <t>Year of publication</t>
   </si>
 </sst>
 </file>
@@ -928,6 +931,9 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>160</v>
+      </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
